--- a/outputs/menu-structure/Hotel_PMS_Menu_Structure.xlsx
+++ b/outputs/menu-structure/Hotel_PMS_Menu_Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI_Project\Hotel_PMS\outputs\menu-structure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B318B5C-2D67-4461-B572-B47949015238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE39EB02-7732-4040-A152-616EA01412AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="요약" sheetId="1" r:id="rId1"/>
@@ -1314,7 +1314,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1337,8 +1337,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1348,124 +1354,113 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFEFE8E3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFEFE8E3"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1476,78 +1471,78 @@
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1555,29 +1550,6 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1592,18 +1564,47 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1621,20 +1622,20 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right/>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1652,22 +1653,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1685,22 +1686,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1718,22 +1719,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1751,22 +1752,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1784,22 +1785,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1817,22 +1818,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1850,22 +1851,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1883,22 +1884,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1917,79 +1918,43 @@
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2006,18 +1971,47 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2035,20 +2029,20 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right/>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2066,22 +2060,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2099,22 +2093,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2132,22 +2126,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2165,22 +2159,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2198,22 +2192,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2231,22 +2225,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2264,22 +2258,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2297,22 +2291,22 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -2331,44 +2325,57 @@
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2397,36 +2404,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DashboardMenu" displayName="DashboardMenu" ref="A5:J49" headerRowDxfId="15" dataDxfId="29" totalsRowDxfId="16" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DashboardMenu" displayName="DashboardMenu" ref="A5:J49" headerRowDxfId="1" dataDxfId="29" totalsRowDxfId="0" headerRowBorderDxfId="12" tableBorderDxfId="13">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="구분" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="레벨" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="메뉴/페이지" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="파일" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="경로" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="유형" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="기능 설명" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="기본 권한" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="비고" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="페이지 상태" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="구분" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="레벨" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="메뉴/페이지" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="파일" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="경로" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="유형" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="기능 설명" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="기본 권한" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="비고" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="페이지 상태" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AdminMenu" displayName="AdminMenu" ref="A5:J24" headerRowDxfId="0" dataDxfId="14" totalsRowDxfId="1" headerRowBorderDxfId="12" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AdminMenu" displayName="AdminMenu" ref="A5:J24" headerRowDxfId="15" dataDxfId="28" totalsRowDxfId="14" headerRowBorderDxfId="26" tableBorderDxfId="27">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="구분" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="레벨" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="메뉴/페이지" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="파일" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="경로" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="유형" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="기능 설명" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="기본 권한" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="비고" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="페이지 상태" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="구분" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="레벨" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="메뉴/페이지" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="파일" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="경로" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="유형" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="기능 설명" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="기본 권한" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="비고" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="페이지 상태" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2599,66 +2606,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2675,18 +2682,18 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="17.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
     </row>
     <row r="5" spans="1:10" ht="16.5">
       <c r="A5" s="1"/>
@@ -2701,86 +2708,86 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="16.5">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="23" t="s">
+      <c r="D6" s="5"/>
+      <c r="E6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="23" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="23" t="s">
+      <c r="J6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="6">
         <v>44</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="24" t="s">
+      <c r="D7" s="7"/>
+      <c r="E7" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="6">
         <v>19</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="24" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="6">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="6">
         <v>28</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="24" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="6">
         <v>12</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="24" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="6">
         <v>6</v>
       </c>
     </row>
@@ -2809,200 +2816,200 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="6" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="24"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="I13" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="6" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.5">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="24"/>
+      <c r="E14" s="6"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="I14" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="6" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H15" s="24" t="s">
+      <c r="H15" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="I15" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="J15" s="24" t="s">
+      <c r="J15" s="6" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="24"/>
+      <c r="E16" s="6"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="6" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="27">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="I17" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="6" t="s">
         <v>351</v>
       </c>
     </row>
@@ -3013,16 +3020,16 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="I18" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="6" t="s">
         <v>351</v>
       </c>
     </row>
@@ -3033,16 +3040,16 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="I19" s="24" t="s">
+      <c r="I19" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="6" t="s">
         <v>351</v>
       </c>
     </row>
@@ -3053,16 +3060,16 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="I20" s="24" t="s">
+      <c r="I20" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="6" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3073,16 +3080,16 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="I21" s="24" t="s">
+      <c r="I21" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="6" t="s">
         <v>363</v>
       </c>
     </row>
@@ -3119,66 +3126,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3206,1443 +3213,1443 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:10" ht="16.5">
+      <c r="A5" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="13" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="15">
         <v>1</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="17" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="15">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="17" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="15">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="15">
         <v>1</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="F9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="15">
         <v>2</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="15">
         <v>1</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="12" t="s">
+      <c r="F11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="15">
         <v>1</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="F12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="15">
         <v>1</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="12" t="s">
+      <c r="F13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="15">
         <v>2</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="15">
         <v>1</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="12" t="s">
+      <c r="F15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="15">
         <v>1</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="F17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="15">
         <v>2</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="15">
         <v>1</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="F19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="15">
         <v>1</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="12" t="s">
+      <c r="F20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="15">
         <v>1</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="12" t="s">
+      <c r="F21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="15">
         <v>1</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22" s="12" t="s">
+      <c r="F22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="15">
         <v>1</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="12" t="s">
+      <c r="F23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J23" s="13" t="s">
+      <c r="J23" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="15">
         <v>2</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="15">
         <v>1</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="12" t="s">
+      <c r="F25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J25" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="15">
         <v>1</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="12" t="s">
+      <c r="F26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="15">
         <v>1</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" s="12" t="s">
+      <c r="F27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J27" s="13" t="s">
+      <c r="J27" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="15">
         <v>1</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28" s="12" t="s">
+      <c r="F28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J28" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="15">
         <v>1</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="F29" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29" s="12" t="s">
+      <c r="F29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="15">
         <v>1</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30" s="12" t="s">
+      <c r="F30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J30" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="15">
         <v>1</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="F31" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="12" t="s">
+      <c r="F31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J31" s="13" t="s">
+      <c r="J31" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="15">
         <v>2</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="15">
         <v>2</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="15">
         <v>2</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="15">
         <v>2</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="15">
         <v>2</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="15">
         <v>2</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="19">
         <v>2</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="H38" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="16" t="s">
+      <c r="I38" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="J38" s="17" t="s">
+      <c r="J38" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="19">
         <v>2</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="G39" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I39" s="16" t="s">
+      <c r="I39" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="J39" s="17" t="s">
+      <c r="J39" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="19">
         <v>1</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F40" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G40" s="16" t="s">
+      <c r="F40" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="H40" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I40" s="16" t="s">
+      <c r="I40" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="17" t="s">
+      <c r="J40" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="19">
         <v>1</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G41" s="16" t="s">
+      <c r="F41" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G41" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="16" t="s">
+      <c r="I41" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J41" s="17" t="s">
+      <c r="J41" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="19">
         <v>1</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="F42" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G42" s="16" t="s">
+      <c r="F42" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I42" s="16" t="s">
+      <c r="I42" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J42" s="17" t="s">
+      <c r="J42" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="19">
         <v>1</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="F43" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G43" s="16" t="s">
+      <c r="F43" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="H43" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I43" s="16" t="s">
+      <c r="I43" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J43" s="17" t="s">
+      <c r="J43" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="19">
         <v>1</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E44" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G44" s="16" t="s">
+      <c r="F44" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H44" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I44" s="16" t="s">
+      <c r="I44" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J44" s="17" t="s">
+      <c r="J44" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="19">
         <v>1</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="16" t="s">
+      <c r="F45" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I45" s="16" t="s">
+      <c r="I45" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J45" s="17" t="s">
+      <c r="J45" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="19">
         <v>1</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="F46" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G46" s="16" t="s">
+      <c r="F46" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G46" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="H46" s="16" t="s">
+      <c r="H46" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I46" s="16" t="s">
+      <c r="I46" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J46" s="17" t="s">
+      <c r="J46" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="19">
         <v>1</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F47" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G47" s="16" t="s">
+      <c r="F47" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="H47" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I47" s="16" t="s">
+      <c r="I47" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J47" s="17" t="s">
+      <c r="J47" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="19">
         <v>1</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E48" s="16" t="s">
+      <c r="E48" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="F48" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G48" s="16" t="s">
+      <c r="F48" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="H48" s="16" t="s">
+      <c r="H48" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="16" t="s">
+      <c r="I48" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="J48" s="17" t="s">
+      <c r="J48" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="22" t="s">
         <v>372</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="23">
         <v>1</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="F49" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G49" s="20" t="s">
+      <c r="F49" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="H49" s="20" t="s">
+      <c r="H49" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="20" t="s">
+      <c r="I49" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="J49" s="21" t="s">
+      <c r="J49" s="25" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4681,66 +4688,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4768,643 +4775,643 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:10" ht="16.5">
+      <c r="A5" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="13" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="15">
         <v>1</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="17" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="15">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="12" t="s">
+      <c r="F7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="15">
         <v>1</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="12" t="s">
+      <c r="F8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="15">
         <v>1</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="F9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="15">
         <v>2</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="15">
         <v>2</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="15">
         <v>1</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="F12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="15">
         <v>1</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="12" t="s">
+      <c r="F13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="15">
         <v>2</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="15">
         <v>2</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="15">
         <v>1</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="F16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="15">
         <v>1</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="F17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="15">
         <v>1</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="12" t="s">
+      <c r="F18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="15">
         <v>1</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="F19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="15">
         <v>1</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="F20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="12" t="s">
+      <c r="F20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="15">
         <v>1</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="12" t="s">
+      <c r="F21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="15">
         <v>1</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22" s="12" t="s">
+      <c r="F22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="19">
         <v>2</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="J23" s="17" t="s">
+      <c r="J23" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="22" t="s">
         <v>373</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="23">
         <v>2</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="24" t="s">
         <v>334</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="24" t="s">
         <v>335</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="24" t="s">
         <v>336</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="J24" s="21" t="s">
+      <c r="J24" s="25" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5438,60 +5445,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5518,22 +5525,22 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="9" t="s">
         <v>52</v>
       </c>
       <c r="G5" s="1"/>
@@ -5541,22 +5548,22 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="27">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="6" t="s">
         <v>192</v>
       </c>
       <c r="G6" s="1"/>
@@ -5564,22 +5571,22 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="27">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="6" t="s">
         <v>192</v>
       </c>
       <c r="G7" s="1"/>
@@ -5587,22 +5594,22 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="27">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="6" t="s">
         <v>192</v>
       </c>
       <c r="G8" s="1"/>
@@ -5610,22 +5617,22 @@
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" ht="27">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="6" t="s">
         <v>192</v>
       </c>
       <c r="G9" s="1"/>
@@ -5633,22 +5640,22 @@
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="27">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="6" t="s">
         <v>192</v>
       </c>
       <c r="G10" s="1"/>
@@ -5656,22 +5663,22 @@
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" ht="40.5">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="6" t="s">
         <v>198</v>
       </c>
       <c r="G11" s="1"/>
@@ -5701,263 +5708,263 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="24" t="s">
+      <c r="H15" s="10"/>
+      <c r="I15" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="24" t="s">
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="24" t="s">
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="H18" s="26"/>
-      <c r="I18" s="24" t="s">
+      <c r="H18" s="10"/>
+      <c r="I18" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26" t="s">
+      <c r="E19" s="10"/>
+      <c r="F19" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="24" t="s">
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17.25">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26" t="s">
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="H20" s="26"/>
-      <c r="I20" s="24" t="s">
+      <c r="H20" s="10"/>
+      <c r="I20" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="24" t="s">
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="24" t="s">
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="24" t="s">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26" t="s">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="I24" s="24" t="s">
+      <c r="I24" s="6" t="s">
         <v>49</v>
       </c>
     </row>
